--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NORTH_CAROLINA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NORTH_CAROLINA_2016.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="6">
@@ -985,7 +985,7 @@
         <v>2</v>
       </c>
       <c r="D35">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="36">
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="D38">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="39">
@@ -1093,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="D41">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="42">
@@ -1525,7 +1525,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="66">
@@ -1741,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="D77">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="78">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="83">
@@ -1867,7 +1867,7 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="85">
@@ -1903,7 +1903,7 @@
         <v>2</v>
       </c>
       <c r="D86">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="87">
@@ -2065,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="96">
@@ -2083,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="D96">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="97">
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="D103">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="104">
@@ -2227,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="105">
@@ -2551,7 +2551,7 @@
         <v>2</v>
       </c>
       <c r="D122">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="123">
@@ -2605,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="D125">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="126">
@@ -2731,7 +2731,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="133">
@@ -2821,7 +2821,7 @@
         <v>2</v>
       </c>
       <c r="D137">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="138">
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="D145">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="146">
@@ -3217,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="D159">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="160">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C167">
@@ -3415,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="D170">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="171">
@@ -3469,7 +3469,7 @@
         <v>19</v>
       </c>
       <c r="D173">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="174">
@@ -3631,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="D182">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="183">
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="D188">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="189">
@@ -3973,7 +3973,7 @@
         <v>2</v>
       </c>
       <c r="D201">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="202">
@@ -4135,7 +4135,7 @@
         <v>2</v>
       </c>
       <c r="D210">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="211">
@@ -4333,7 +4333,7 @@
         <v>2</v>
       </c>
       <c r="D221">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="222">
@@ -4369,7 +4369,7 @@
         <v>2</v>
       </c>
       <c r="D223">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="224">
@@ -4423,7 +4423,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="227">
@@ -4513,7 +4513,7 @@
         <v>2</v>
       </c>
       <c r="D231">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="232">
@@ -4927,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="D254">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="255">
@@ -4963,7 +4963,7 @@
         <v>2</v>
       </c>
       <c r="D256">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="257">
@@ -5089,7 +5089,7 @@
         <v>2</v>
       </c>
       <c r="D263">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="264">
@@ -5161,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="D267">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="268">
@@ -5197,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="D269">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="270">
@@ -5215,7 +5215,7 @@
         <v>2</v>
       </c>
       <c r="D270">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="271">
@@ -5287,7 +5287,7 @@
         <v>2</v>
       </c>
       <c r="D274">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="275">
@@ -5467,7 +5467,7 @@
         <v>2</v>
       </c>
       <c r="D284">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="285">
@@ -5521,7 +5521,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="288">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C304">
@@ -6241,7 +6241,7 @@
         <v>2</v>
       </c>
       <c r="D327">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="328">
@@ -6457,7 +6457,7 @@
         <v>19</v>
       </c>
       <c r="D339">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="340">
@@ -6637,7 +6637,7 @@
         <v>2</v>
       </c>
       <c r="D349">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="350">
@@ -6871,7 +6871,7 @@
         <v>2</v>
       </c>
       <c r="D362">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="363">
@@ -6907,7 +6907,7 @@
         <v>19</v>
       </c>
       <c r="D364">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="365">
@@ -7159,7 +7159,7 @@
         <v>2</v>
       </c>
       <c r="D378">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="379">
@@ -7177,7 +7177,7 @@
         <v>2</v>
       </c>
       <c r="D379">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="380">
@@ -7591,7 +7591,7 @@
         <v>19</v>
       </c>
       <c r="D402">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="403">
@@ -7861,7 +7861,7 @@
         <v>2</v>
       </c>
       <c r="D417">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="418">
@@ -7879,7 +7879,7 @@
         <v>2</v>
       </c>
       <c r="D418">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="419">
@@ -7951,7 +7951,7 @@
         <v>2</v>
       </c>
       <c r="D422">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="423">
@@ -8023,7 +8023,7 @@
         <v>2</v>
       </c>
       <c r="D426">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="427">
@@ -8041,7 +8041,7 @@
         <v>2</v>
       </c>
       <c r="D427">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="428">
@@ -8113,7 +8113,7 @@
         <v>2</v>
       </c>
       <c r="D431">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="432">
@@ -8347,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="D444">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="445">
@@ -8401,7 +8401,7 @@
         <v>2</v>
       </c>
       <c r="D447">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="448">
@@ -8635,7 +8635,7 @@
         <v>2</v>
       </c>
       <c r="D460">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="461">
@@ -8833,7 +8833,7 @@
         <v>2</v>
       </c>
       <c r="D471">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="472">
@@ -8851,7 +8851,7 @@
         <v>2</v>
       </c>
       <c r="D472">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="473">
@@ -9049,7 +9049,7 @@
         <v>2</v>
       </c>
       <c r="D483">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="484">
@@ -9337,7 +9337,7 @@
         <v>2</v>
       </c>
       <c r="D499">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="500">
@@ -9535,7 +9535,7 @@
         <v>2</v>
       </c>
       <c r="D510">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="511">
@@ -9553,7 +9553,7 @@
         <v>2</v>
       </c>
       <c r="D511">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="512">
@@ -9571,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="D512">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="513">
@@ -9715,7 +9715,7 @@
         <v>2</v>
       </c>
       <c r="D520">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="521">
@@ -9823,7 +9823,7 @@
         <v>2</v>
       </c>
       <c r="D526">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="527">
@@ -9895,7 +9895,7 @@
         <v>2</v>
       </c>
       <c r="D530">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="531">
@@ -10057,7 +10057,7 @@
         <v>2</v>
       </c>
       <c r="D539">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="540">
@@ -10147,7 +10147,7 @@
         <v>2</v>
       </c>
       <c r="D544">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="545">
@@ -10453,7 +10453,7 @@
         <v>2</v>
       </c>
       <c r="D561">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="562">
@@ -10723,7 +10723,7 @@
         <v>2</v>
       </c>
       <c r="D576">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="577">
@@ -10831,7 +10831,7 @@
         <v>2</v>
       </c>
       <c r="D582">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="583">
@@ -11011,7 +11011,7 @@
         <v>2</v>
       </c>
       <c r="D592">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="593">
@@ -11119,7 +11119,7 @@
         <v>2</v>
       </c>
       <c r="D598">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="599">
@@ -11425,7 +11425,7 @@
         <v>2</v>
       </c>
       <c r="D615">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="616">
@@ -11443,7 +11443,7 @@
         <v>2</v>
       </c>
       <c r="D616">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="617">
@@ -11839,7 +11839,7 @@
         <v>2</v>
       </c>
       <c r="D638">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="639">
@@ -11983,7 +11983,7 @@
         <v>2</v>
       </c>
       <c r="D646">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="647">
@@ -12001,7 +12001,7 @@
         <v>2</v>
       </c>
       <c r="D647">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="648">
@@ -12019,7 +12019,7 @@
         <v>19</v>
       </c>
       <c r="D648">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="649">
@@ -12163,7 +12163,7 @@
         <v>2</v>
       </c>
       <c r="D656">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="657">
@@ -12235,7 +12235,7 @@
         <v>2</v>
       </c>
       <c r="D660">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="661">
@@ -12307,7 +12307,7 @@
         <v>2</v>
       </c>
       <c r="D664">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="665">
@@ -12487,7 +12487,7 @@
         <v>2</v>
       </c>
       <c r="D674">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="675">
@@ -12811,7 +12811,7 @@
         <v>2</v>
       </c>
       <c r="D692">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="693">
@@ -13135,7 +13135,7 @@
         <v>2</v>
       </c>
       <c r="D710">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="711">
@@ -13171,7 +13171,7 @@
         <v>2</v>
       </c>
       <c r="D712">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="713">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C716">
@@ -13261,7 +13261,7 @@
         <v>2</v>
       </c>
       <c r="D717">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13495,7 +13495,7 @@
         <v>2</v>
       </c>
       <c r="D730">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="731">
@@ -14251,7 +14251,7 @@
         <v>2</v>
       </c>
       <c r="D772">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="773">
@@ -14269,7 +14269,7 @@
         <v>2</v>
       </c>
       <c r="D773">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="774">
@@ -14305,7 +14305,7 @@
         <v>19</v>
       </c>
       <c r="D775">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="776">
@@ -14323,7 +14323,7 @@
         <v>2</v>
       </c>
       <c r="D776">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="777">
@@ -14395,7 +14395,7 @@
         <v>2</v>
       </c>
       <c r="D780">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="781">
@@ -14431,7 +14431,7 @@
         <v>2</v>
       </c>
       <c r="D782">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="783">
@@ -14575,7 +14575,7 @@
         <v>2</v>
       </c>
       <c r="D790">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="791">
@@ -14611,7 +14611,7 @@
         <v>2</v>
       </c>
       <c r="D792">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="793">
@@ -14737,7 +14737,7 @@
         <v>2</v>
       </c>
       <c r="D799">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="800">
@@ -14755,7 +14755,7 @@
         <v>2</v>
       </c>
       <c r="D800">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="801">
@@ -14953,7 +14953,7 @@
         <v>2</v>
       </c>
       <c r="D811">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="812">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C818">
@@ -15097,7 +15097,7 @@
         <v>2</v>
       </c>
       <c r="D819">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="820">
@@ -15133,7 +15133,7 @@
         <v>2</v>
       </c>
       <c r="D821">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="822">
@@ -15223,7 +15223,7 @@
         <v>2</v>
       </c>
       <c r="D826">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="827">
@@ -15241,7 +15241,7 @@
         <v>2</v>
       </c>
       <c r="D827">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="828">
@@ -15259,7 +15259,7 @@
         <v>2</v>
       </c>
       <c r="D828">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="829">
@@ -15619,7 +15619,7 @@
         <v>2</v>
       </c>
       <c r="D848">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="849">
@@ -15727,7 +15727,7 @@
         <v>2</v>
       </c>
       <c r="D854">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="855">
@@ -15745,7 +15745,7 @@
         <v>2</v>
       </c>
       <c r="D855">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="856">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C857">
@@ -15799,7 +15799,7 @@
         <v>2</v>
       </c>
       <c r="D858">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="859">
@@ -15871,7 +15871,7 @@
         <v>2</v>
       </c>
       <c r="D862">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="863">
@@ -16069,7 +16069,7 @@
         <v>2</v>
       </c>
       <c r="D873">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="874">
@@ -16087,7 +16087,7 @@
         <v>2</v>
       </c>
       <c r="D874">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="875">
@@ -16159,7 +16159,7 @@
         <v>2</v>
       </c>
       <c r="D878">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="879">
@@ -16339,7 +16339,7 @@
         <v>2</v>
       </c>
       <c r="D888">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="889">
@@ -16501,7 +16501,7 @@
         <v>2</v>
       </c>
       <c r="D897">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="898">
@@ -16537,7 +16537,7 @@
         <v>19</v>
       </c>
       <c r="D899">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="900">
@@ -16573,7 +16573,7 @@
         <v>2</v>
       </c>
       <c r="D901">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="902">
@@ -16645,7 +16645,7 @@
         <v>2</v>
       </c>
       <c r="D905">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="906">
@@ -16861,7 +16861,7 @@
         <v>2</v>
       </c>
       <c r="D917">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="918">
@@ -17293,7 +17293,7 @@
         <v>19</v>
       </c>
       <c r="D941">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="942">
@@ -17419,7 +17419,7 @@
         <v>19</v>
       </c>
       <c r="D948">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="949">
@@ -17509,7 +17509,7 @@
         <v>19</v>
       </c>
       <c r="D953">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="954">
@@ -17563,7 +17563,7 @@
         <v>2</v>
       </c>
       <c r="D956">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="957">
@@ -17689,7 +17689,7 @@
         <v>2</v>
       </c>
       <c r="D963">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="964">
@@ -17707,7 +17707,7 @@
         <v>2</v>
       </c>
       <c r="D964">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="965">
@@ -17779,7 +17779,7 @@
         <v>2</v>
       </c>
       <c r="D968">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="969">
@@ -17869,7 +17869,7 @@
         <v>2</v>
       </c>
       <c r="D973">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="974">
@@ -17923,7 +17923,7 @@
         <v>2</v>
       </c>
       <c r="D976">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="977">
@@ -18103,7 +18103,7 @@
         <v>2</v>
       </c>
       <c r="D986">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="987">
@@ -18157,7 +18157,7 @@
         <v>2</v>
       </c>
       <c r="D989">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="990">
@@ -18301,7 +18301,7 @@
         <v>2</v>
       </c>
       <c r="D997">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="998">
@@ -18373,7 +18373,7 @@
         <v>2</v>
       </c>
       <c r="D1001">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18553,7 +18553,7 @@
         <v>2</v>
       </c>
       <c r="D1011">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1012">
@@ -18589,7 +18589,7 @@
         <v>2</v>
       </c>
       <c r="D1013">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1014">
@@ -18607,7 +18607,7 @@
         <v>2</v>
       </c>
       <c r="D1014">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1015">
@@ -18643,7 +18643,7 @@
         <v>2</v>
       </c>
       <c r="D1016">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1017">
@@ -18841,7 +18841,7 @@
         <v>2</v>
       </c>
       <c r="D1027">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1028">
@@ -18895,7 +18895,7 @@
         <v>2</v>
       </c>
       <c r="D1030">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1031">
@@ -19003,7 +19003,7 @@
         <v>2</v>
       </c>
       <c r="D1036">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1037">
@@ -19057,7 +19057,7 @@
         <v>2</v>
       </c>
       <c r="D1039">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1040">
@@ -19129,7 +19129,7 @@
         <v>2</v>
       </c>
       <c r="D1043">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1044">
@@ -19237,7 +19237,7 @@
         <v>2</v>
       </c>
       <c r="D1049">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1050">
@@ -19291,7 +19291,7 @@
         <v>2</v>
       </c>
       <c r="D1052">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1053">
@@ -19327,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="D1054">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19489,7 +19489,7 @@
         <v>2</v>
       </c>
       <c r="D1063">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1064">
@@ -19615,7 +19615,7 @@
         <v>2</v>
       </c>
       <c r="D1070">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1071">
@@ -19687,7 +19687,7 @@
         <v>2</v>
       </c>
       <c r="D1074">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1075">
@@ -19849,7 +19849,7 @@
         <v>2</v>
       </c>
       <c r="D1083">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1084">
@@ -19975,7 +19975,7 @@
         <v>2</v>
       </c>
       <c r="D1090">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1091">
@@ -20227,7 +20227,7 @@
         <v>2</v>
       </c>
       <c r="D1104">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1105">
@@ -20245,7 +20245,7 @@
         <v>2</v>
       </c>
       <c r="D1105">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1106">
@@ -20335,7 +20335,7 @@
         <v>19</v>
       </c>
       <c r="D1110">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="1111">
@@ -20389,7 +20389,7 @@
         <v>2</v>
       </c>
       <c r="D1113">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1114">
@@ -20551,7 +20551,7 @@
         <v>2</v>
       </c>
       <c r="D1122">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1123">
@@ -20947,7 +20947,7 @@
         <v>2</v>
       </c>
       <c r="D1144">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1145">
@@ -21073,7 +21073,7 @@
         <v>2</v>
       </c>
       <c r="D1151">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1152">
@@ -21307,7 +21307,7 @@
         <v>2</v>
       </c>
       <c r="D1164">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1165">
@@ -21433,7 +21433,7 @@
         <v>2</v>
       </c>
       <c r="D1171">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1172">
@@ -21487,7 +21487,7 @@
         <v>2</v>
       </c>
       <c r="D1174">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1175">
@@ -21505,7 +21505,7 @@
         <v>2</v>
       </c>
       <c r="D1175">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1176">
@@ -21523,7 +21523,7 @@
         <v>2</v>
       </c>
       <c r="D1176">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1177">
@@ -21667,7 +21667,7 @@
         <v>2</v>
       </c>
       <c r="D1184">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1185">
@@ -21703,7 +21703,7 @@
         <v>2</v>
       </c>
       <c r="D1186">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1187">
@@ -21775,7 +21775,7 @@
         <v>2</v>
       </c>
       <c r="D1190">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1191">
@@ -21829,7 +21829,7 @@
         <v>2</v>
       </c>
       <c r="D1193">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1194">
@@ -22153,7 +22153,7 @@
         <v>2</v>
       </c>
       <c r="D1211">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1212">
@@ -22495,7 +22495,7 @@
         <v>2</v>
       </c>
       <c r="D1230">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1231">
@@ -22549,7 +22549,7 @@
         <v>2</v>
       </c>
       <c r="D1233">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1234">
@@ -22567,7 +22567,7 @@
         <v>2</v>
       </c>
       <c r="D1234">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1235">
@@ -22621,7 +22621,7 @@
         <v>2</v>
       </c>
       <c r="D1237">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1238">
@@ -22639,7 +22639,7 @@
         <v>2</v>
       </c>
       <c r="D1238">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1239">
@@ -22693,7 +22693,7 @@
         <v>2</v>
       </c>
       <c r="D1241">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1242">
@@ -22729,7 +22729,7 @@
         <v>2</v>
       </c>
       <c r="D1243">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1244">
@@ -22837,7 +22837,7 @@
         <v>2</v>
       </c>
       <c r="D1249">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1250">
@@ -22909,7 +22909,7 @@
         <v>2</v>
       </c>
       <c r="D1253">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1254">
@@ -23071,7 +23071,7 @@
         <v>2</v>
       </c>
       <c r="D1262">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1263">
@@ -23197,7 +23197,7 @@
         <v>2</v>
       </c>
       <c r="D1269">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1270">
@@ -23431,7 +23431,7 @@
         <v>2</v>
       </c>
       <c r="D1282">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1283">
@@ -23539,7 +23539,7 @@
         <v>2</v>
       </c>
       <c r="D1288">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1289">
@@ -23629,7 +23629,7 @@
         <v>2</v>
       </c>
       <c r="D1293">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1294">
@@ -23647,7 +23647,7 @@
         <v>2</v>
       </c>
       <c r="D1294">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1295">
@@ -23827,7 +23827,7 @@
         <v>2</v>
       </c>
       <c r="D1304">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1305">
@@ -24115,7 +24115,7 @@
         <v>2</v>
       </c>
       <c r="D1320">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1321">
@@ -24475,7 +24475,7 @@
         <v>19</v>
       </c>
       <c r="D1340">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="1341">
@@ -24547,7 +24547,7 @@
         <v>2</v>
       </c>
       <c r="D1344">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1345">
@@ -24727,7 +24727,7 @@
         <v>2</v>
       </c>
       <c r="D1354">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1355">
@@ -24781,7 +24781,7 @@
         <v>19</v>
       </c>
       <c r="D1357">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="1358">
@@ -24835,7 +24835,7 @@
         <v>2</v>
       </c>
       <c r="D1360">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1361">
@@ -24961,7 +24961,7 @@
         <v>2</v>
       </c>
       <c r="D1367">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1368">
@@ -25195,7 +25195,7 @@
         <v>2</v>
       </c>
       <c r="D1380">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1381">
@@ -25249,7 +25249,7 @@
         <v>2</v>
       </c>
       <c r="D1383">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1384">
@@ -25267,7 +25267,7 @@
         <v>2</v>
       </c>
       <c r="D1384">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1385">
@@ -25339,7 +25339,7 @@
         <v>19</v>
       </c>
       <c r="D1388">
-        <v>0.0009252495738982225</v>
+        <v>0.0009252495738982224</v>
       </c>
     </row>
     <row r="1389">
@@ -25609,7 +25609,7 @@
         <v>2</v>
       </c>
       <c r="D1403">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1404">
@@ -25699,7 +25699,7 @@
         <v>2</v>
       </c>
       <c r="D1408">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1409">
@@ -26023,7 +26023,7 @@
         <v>2</v>
       </c>
       <c r="D1426">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1427">
@@ -26239,7 +26239,7 @@
         <v>2</v>
       </c>
       <c r="D1438">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1439">
@@ -26329,7 +26329,7 @@
         <v>2</v>
       </c>
       <c r="D1443">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1444">
@@ -26347,7 +26347,7 @@
         <v>2</v>
       </c>
       <c r="D1444">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1445">
@@ -26401,7 +26401,7 @@
         <v>2</v>
       </c>
       <c r="D1447">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1448">
@@ -26527,7 +26527,7 @@
         <v>2</v>
       </c>
       <c r="D1454">
-        <v>9.739469198928659E-05</v>
+        <v>9.73946919892866E-05</v>
       </c>
     </row>
     <row r="1455">
